--- a/backend/data/financials_by_company/0Q8.F.xlsx
+++ b/backend/data/financials_by_company/0Q8.F.xlsx
@@ -692,225 +692,215 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-3705570</v>
+        <v>-1053930</v>
       </c>
       <c r="C2" t="n">
         <v>0.19</v>
       </c>
       <c r="D2" t="n">
-        <v>48862000</v>
+        <v>17476000</v>
       </c>
       <c r="E2" t="n">
-        <v>-19503000</v>
+        <v>-5547000</v>
       </c>
       <c r="F2" t="n">
-        <v>-19503000</v>
+        <v>-5547000</v>
       </c>
       <c r="G2" t="n">
-        <v>-34415000</v>
+        <v>-22837000</v>
       </c>
       <c r="H2" t="n">
-        <v>14852000</v>
+        <v>14692000</v>
       </c>
       <c r="I2" t="n">
-        <v>98802000</v>
+        <v>332303000</v>
       </c>
       <c r="J2" t="n">
-        <v>29359000</v>
+        <v>11929000</v>
       </c>
       <c r="K2" t="n">
-        <v>14507000</v>
+        <v>-2763000</v>
       </c>
       <c r="L2" t="n">
-        <v>-45872000</v>
+        <v>-9822000</v>
       </c>
       <c r="M2" t="n">
-        <v>39077000</v>
+        <v>12360000</v>
       </c>
       <c r="N2" t="n">
-        <v>1633000</v>
+        <v>3023000</v>
       </c>
       <c r="O2" t="n">
-        <v>-18617570</v>
+        <v>-18343930</v>
       </c>
       <c r="P2" t="n">
-        <v>-34415000</v>
+        <v>-22837000</v>
       </c>
       <c r="Q2" t="n">
-        <v>291757000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>3614000</v>
-      </c>
+        <v>699384000</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>19815000</v>
+        <v>-1070000</v>
       </c>
       <c r="T2" t="n">
-        <v>68773650</v>
+        <v>68731815</v>
       </c>
       <c r="U2" t="n">
-        <v>68773650</v>
+        <v>65378958</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.5</v>
+        <v>-0.35</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.5</v>
+        <v>-0.35</v>
       </c>
       <c r="X2" t="n">
-        <v>-34415000</v>
+        <v>-22837000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-34415000</v>
+        <v>-22837000</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-34415000</v>
+        <v>-22837000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-151000</v>
+        <v>-6425000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-34264000</v>
+        <v>-16412000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-34264000</v>
+        <v>-16412000</v>
       </c>
       <c r="AE2" t="n">
-        <v>9694000</v>
+        <v>1289000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-24570000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-2644000</v>
-      </c>
+        <v>-15123000</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>-16807000</v>
+        <v>-4316000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-4422000</v>
+        <v>-104000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>14021000</v>
+        <v>4060000</v>
       </c>
       <c r="AK2" t="n">
-        <v>7208000</v>
+        <v>360000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-45872000</v>
+        <v>-9822000</v>
       </c>
       <c r="AM2" t="n">
-        <v>8428000</v>
+        <v>485000</v>
       </c>
       <c r="AN2" t="n">
-        <v>39077000</v>
+        <v>12360000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1633000</v>
+        <v>3023000</v>
       </c>
       <c r="AP2" t="n">
-        <v>49797000</v>
+        <v>5924000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>192955000</v>
+        <v>367081000</v>
       </c>
       <c r="AR2" t="n">
-        <v>122636000</v>
+        <v>242366000</v>
       </c>
       <c r="AS2" t="n">
-        <v>14852000</v>
+        <v>14692000</v>
       </c>
       <c r="AT2" t="n">
-        <v>14852000</v>
+        <v>14692000</v>
       </c>
       <c r="AU2" t="n">
-        <v>5758000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>5520000</v>
-      </c>
+        <v>220095000</v>
+      </c>
+      <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="n">
-        <v>238000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3614000</v>
-      </c>
+        <v>220095000</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="n">
-        <v>242752000</v>
+        <v>373005000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>98802000</v>
+        <v>332303000</v>
       </c>
       <c r="BA2" t="n">
-        <v>341554000</v>
+        <v>705308000</v>
       </c>
       <c r="BB2" t="n">
-        <v>341554000</v>
+        <v>705308000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>235696.92978</v>
+        <v>-394268.518368</v>
       </c>
       <c r="C3" t="n">
-        <v>0.018948</v>
+        <v>0.084898</v>
       </c>
       <c r="D3" t="n">
-        <v>-29418000</v>
+        <v>-57918000</v>
       </c>
       <c r="E3" t="n">
-        <v>12439000</v>
+        <v>-4644000</v>
       </c>
       <c r="F3" t="n">
-        <v>12439000</v>
+        <v>-4644000</v>
       </c>
       <c r="G3" t="n">
-        <v>-65572000</v>
+        <v>-111894000</v>
       </c>
       <c r="H3" t="n">
-        <v>13755000</v>
+        <v>21539000</v>
       </c>
       <c r="I3" t="n">
-        <v>270902000</v>
+        <v>332351000</v>
       </c>
       <c r="J3" t="n">
-        <v>-16979000</v>
+        <v>-62562000</v>
       </c>
       <c r="K3" t="n">
-        <v>-30734000</v>
+        <v>-84101000</v>
       </c>
       <c r="L3" t="n">
-        <v>-51198000</v>
+        <v>-41898000</v>
       </c>
       <c r="M3" t="n">
-        <v>38349000</v>
+        <v>39317000</v>
       </c>
       <c r="N3" t="n">
-        <v>1610000</v>
+        <v>3226000</v>
       </c>
       <c r="O3" t="n">
-        <v>-77775303.07021999</v>
+        <v>-107644268.518368</v>
       </c>
       <c r="P3" t="n">
-        <v>-65572000</v>
+        <v>-111894000</v>
       </c>
       <c r="Q3" t="n">
-        <v>478729000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>7112000</v>
-      </c>
+        <v>677602000</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>-32328000</v>
+        <v>-75542000</v>
       </c>
       <c r="T3" t="n">
         <v>68773650</v>
@@ -919,160 +909,158 @@
         <v>68773650</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.95</v>
+        <v>-1.63</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.95</v>
+        <v>-1.63</v>
       </c>
       <c r="X3" t="n">
-        <v>-65572000</v>
+        <v>-111894000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-65572000</v>
+        <v>-111894000</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-65572000</v>
+        <v>-111894000</v>
       </c>
       <c r="AB3" t="n">
-        <v>2202000</v>
+        <v>1046000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-67774000</v>
+        <v>-112940000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-67774000</v>
+        <v>-112940000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-1309000</v>
+        <v>-10478000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-69083000</v>
+        <v>-123418000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-8379000</v>
+        <v>-1814000</v>
       </c>
       <c r="AH3" t="n">
-        <v>19022000</v>
+        <v>-2953000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-14435000</v>
+        <v>-9821000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-5903000</v>
+        <v>8541000</v>
       </c>
       <c r="AK3" t="n">
-        <v>1316000</v>
+        <v>1198000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-51198000</v>
+        <v>-41898000</v>
       </c>
       <c r="AM3" t="n">
-        <v>14459000</v>
+        <v>5807000</v>
       </c>
       <c r="AN3" t="n">
-        <v>38349000</v>
+        <v>39317000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1610000</v>
+        <v>3226000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-22188000</v>
+        <v>-74169000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>207827000</v>
+        <v>345251000</v>
       </c>
       <c r="AR3" t="n">
-        <v>112656000</v>
+        <v>225901000</v>
       </c>
       <c r="AS3" t="n">
-        <v>13755000</v>
+        <v>21539000</v>
       </c>
       <c r="AT3" t="n">
-        <v>13755000</v>
+        <v>21539000</v>
       </c>
       <c r="AU3" t="n">
-        <v>12197000</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>11917000</v>
-      </c>
+        <v>468000</v>
+      </c>
+      <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="n">
-        <v>280000</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>7112000</v>
-      </c>
+        <v>468000</v>
+      </c>
+      <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="n">
-        <v>185639000</v>
+        <v>271082000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>270902000</v>
+        <v>332351000</v>
       </c>
       <c r="BA3" t="n">
-        <v>456541000</v>
+        <v>603433000</v>
       </c>
       <c r="BB3" t="n">
-        <v>456541000</v>
+        <v>603433000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-394268.518368</v>
+        <v>235696.92978</v>
       </c>
       <c r="C4" t="n">
-        <v>0.084898</v>
+        <v>0.018948</v>
       </c>
       <c r="D4" t="n">
-        <v>-57918000</v>
+        <v>-29418000</v>
       </c>
       <c r="E4" t="n">
-        <v>-4644000</v>
+        <v>12439000</v>
       </c>
       <c r="F4" t="n">
-        <v>-4644000</v>
+        <v>12439000</v>
       </c>
       <c r="G4" t="n">
-        <v>-111894000</v>
+        <v>-65572000</v>
       </c>
       <c r="H4" t="n">
-        <v>21539000</v>
+        <v>13755000</v>
       </c>
       <c r="I4" t="n">
-        <v>332351000</v>
+        <v>270902000</v>
       </c>
       <c r="J4" t="n">
-        <v>-62562000</v>
+        <v>-16979000</v>
       </c>
       <c r="K4" t="n">
-        <v>-84101000</v>
+        <v>-30734000</v>
       </c>
       <c r="L4" t="n">
-        <v>-41898000</v>
+        <v>-51198000</v>
       </c>
       <c r="M4" t="n">
-        <v>39317000</v>
+        <v>38349000</v>
       </c>
       <c r="N4" t="n">
-        <v>3226000</v>
+        <v>1610000</v>
       </c>
       <c r="O4" t="n">
-        <v>-107644268.518368</v>
+        <v>-77775303.07021999</v>
       </c>
       <c r="P4" t="n">
-        <v>-111894000</v>
+        <v>-65572000</v>
       </c>
       <c r="Q4" t="n">
-        <v>677602000</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
+        <v>478729000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7112000</v>
+      </c>
       <c r="S4" t="n">
-        <v>-75542000</v>
+        <v>-32328000</v>
       </c>
       <c r="T4" t="n">
         <v>68773650</v>
@@ -1081,255 +1069,267 @@
         <v>68773650</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.63</v>
+        <v>-0.95</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.63</v>
+        <v>-0.95</v>
       </c>
       <c r="X4" t="n">
-        <v>-111894000</v>
+        <v>-65572000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-111894000</v>
+        <v>-65572000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-111894000</v>
+        <v>-65572000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1046000</v>
+        <v>2202000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-112940000</v>
+        <v>-67774000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-112940000</v>
+        <v>-67774000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-10478000</v>
+        <v>-1309000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-123418000</v>
+        <v>-69083000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1814000</v>
+        <v>-8379000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-2953000</v>
+        <v>19022000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-9821000</v>
+        <v>-14435000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>8541000</v>
+        <v>-5903000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1198000</v>
+        <v>1316000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-41898000</v>
+        <v>-51198000</v>
       </c>
       <c r="AM4" t="n">
-        <v>5807000</v>
+        <v>14459000</v>
       </c>
       <c r="AN4" t="n">
-        <v>39317000</v>
+        <v>38349000</v>
       </c>
       <c r="AO4" t="n">
-        <v>3226000</v>
+        <v>1610000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-74169000</v>
+        <v>-22188000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>345251000</v>
+        <v>207827000</v>
       </c>
       <c r="AR4" t="n">
-        <v>225901000</v>
+        <v>112656000</v>
       </c>
       <c r="AS4" t="n">
-        <v>21539000</v>
+        <v>13755000</v>
       </c>
       <c r="AT4" t="n">
-        <v>21539000</v>
+        <v>13755000</v>
       </c>
       <c r="AU4" t="n">
-        <v>468000</v>
-      </c>
-      <c r="AV4" t="inlineStr"/>
+        <v>12197000</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>11917000</v>
+      </c>
       <c r="AW4" t="n">
-        <v>468000</v>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+        <v>280000</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>7112000</v>
+      </c>
       <c r="AY4" t="n">
-        <v>271082000</v>
+        <v>185639000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>332351000</v>
+        <v>270902000</v>
       </c>
       <c r="BA4" t="n">
-        <v>603433000</v>
+        <v>456541000</v>
       </c>
       <c r="BB4" t="n">
-        <v>603433000</v>
+        <v>456541000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-1053930</v>
+        <v>-3705570</v>
       </c>
       <c r="C5" t="n">
         <v>0.19</v>
       </c>
       <c r="D5" t="n">
-        <v>17476000</v>
+        <v>48862000</v>
       </c>
       <c r="E5" t="n">
-        <v>-5547000</v>
+        <v>-19503000</v>
       </c>
       <c r="F5" t="n">
-        <v>-5547000</v>
+        <v>-19503000</v>
       </c>
       <c r="G5" t="n">
-        <v>-22837000</v>
+        <v>-34415000</v>
       </c>
       <c r="H5" t="n">
-        <v>14692000</v>
+        <v>14852000</v>
       </c>
       <c r="I5" t="n">
-        <v>332303000</v>
+        <v>98802000</v>
       </c>
       <c r="J5" t="n">
-        <v>11929000</v>
+        <v>29359000</v>
       </c>
       <c r="K5" t="n">
-        <v>-2763000</v>
+        <v>14507000</v>
       </c>
       <c r="L5" t="n">
-        <v>-9822000</v>
+        <v>-45872000</v>
       </c>
       <c r="M5" t="n">
-        <v>12360000</v>
+        <v>39077000</v>
       </c>
       <c r="N5" t="n">
-        <v>3023000</v>
+        <v>1633000</v>
       </c>
       <c r="O5" t="n">
-        <v>-18343930</v>
+        <v>-18617570</v>
       </c>
       <c r="P5" t="n">
-        <v>-22837000</v>
+        <v>-34415000</v>
       </c>
       <c r="Q5" t="n">
-        <v>699384000</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>291757000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3614000</v>
+      </c>
       <c r="S5" t="n">
-        <v>-1070000</v>
+        <v>19815000</v>
       </c>
       <c r="T5" t="n">
-        <v>68731815</v>
+        <v>68773650</v>
       </c>
       <c r="U5" t="n">
-        <v>65378958</v>
+        <v>68773650</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.35</v>
+        <v>-0.5</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.35</v>
+        <v>-0.5</v>
       </c>
       <c r="X5" t="n">
-        <v>-22837000</v>
+        <v>-34415000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-22837000</v>
+        <v>-34415000</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-22837000</v>
+        <v>-34415000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-6425000</v>
+        <v>-151000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-16412000</v>
+        <v>-34264000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-16412000</v>
+        <v>-34264000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1289000</v>
+        <v>9694000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-15123000</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
+        <v>-24570000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-2644000</v>
+      </c>
       <c r="AH5" t="n">
-        <v>-4316000</v>
+        <v>-16807000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-104000</v>
+        <v>-4422000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4060000</v>
+        <v>14021000</v>
       </c>
       <c r="AK5" t="n">
-        <v>360000</v>
+        <v>7208000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-9822000</v>
+        <v>-45872000</v>
       </c>
       <c r="AM5" t="n">
-        <v>485000</v>
+        <v>8428000</v>
       </c>
       <c r="AN5" t="n">
-        <v>12360000</v>
+        <v>39077000</v>
       </c>
       <c r="AO5" t="n">
-        <v>3023000</v>
+        <v>1633000</v>
       </c>
       <c r="AP5" t="n">
-        <v>5924000</v>
+        <v>49797000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>367081000</v>
+        <v>192955000</v>
       </c>
       <c r="AR5" t="n">
-        <v>242366000</v>
+        <v>122636000</v>
       </c>
       <c r="AS5" t="n">
-        <v>14692000</v>
+        <v>14852000</v>
       </c>
       <c r="AT5" t="n">
-        <v>14692000</v>
+        <v>14852000</v>
       </c>
       <c r="AU5" t="n">
-        <v>220095000</v>
-      </c>
-      <c r="AV5" t="inlineStr"/>
+        <v>5758000</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>5520000</v>
+      </c>
       <c r="AW5" t="n">
-        <v>220095000</v>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+        <v>238000</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>3614000</v>
+      </c>
       <c r="AY5" t="n">
-        <v>373005000</v>
+        <v>242752000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>332303000</v>
+        <v>98802000</v>
       </c>
       <c r="BA5" t="n">
-        <v>705308000</v>
+        <v>341554000</v>
       </c>
       <c r="BB5" t="n">
-        <v>705308000</v>
+        <v>341554000</v>
       </c>
     </row>
   </sheetData>
@@ -1740,7 +1740,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>68773650</v>
@@ -1749,47 +1749,49 @@
         <v>68773650</v>
       </c>
       <c r="D2" t="n">
-        <v>489170000</v>
+        <v>389914000</v>
       </c>
       <c r="E2" t="n">
-        <v>533484000</v>
+        <v>500870000</v>
       </c>
       <c r="F2" t="n">
-        <v>-106362000</v>
+        <v>122303000</v>
       </c>
       <c r="G2" t="n">
-        <v>419442000</v>
+        <v>582337000</v>
       </c>
       <c r="H2" t="n">
-        <v>-496183000</v>
+        <v>-196515000</v>
       </c>
       <c r="I2" t="n">
-        <v>-106362000</v>
+        <v>122303000</v>
       </c>
       <c r="J2" t="n">
-        <v>34939000</v>
+        <v>49569000</v>
       </c>
       <c r="K2" t="n">
-        <v>-79103000</v>
+        <v>131036000</v>
       </c>
       <c r="L2" t="n">
-        <v>-74636000</v>
+        <v>247516000</v>
       </c>
       <c r="M2" t="n">
-        <v>-78592000</v>
+        <v>130771000</v>
       </c>
       <c r="N2" t="n">
-        <v>511000</v>
+        <v>-265000</v>
       </c>
       <c r="O2" t="n">
-        <v>-79103000</v>
+        <v>131036000</v>
       </c>
       <c r="P2" t="n">
         <v>-31004000</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
       <c r="R2" t="n">
-        <v>-182697000</v>
+        <v>27442000</v>
       </c>
       <c r="S2" t="n">
         <v>4616000</v>
@@ -1801,173 +1803,183 @@
         <v>129982000</v>
       </c>
       <c r="V2" t="n">
-        <v>694027000</v>
+        <v>684422000</v>
       </c>
       <c r="W2" t="n">
-        <v>42195000</v>
+        <v>181646000</v>
       </c>
       <c r="X2" t="n">
-        <v>542000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>14238000</v>
+      </c>
       <c r="Z2" t="n">
-        <v>68000</v>
+        <v>64000</v>
       </c>
       <c r="AA2" t="n">
-        <v>2980000</v>
+        <v>2232000</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>32935000</v>
+        <v>156902000</v>
       </c>
       <c r="AD2" t="n">
-        <v>28468000</v>
+        <v>40422000</v>
       </c>
       <c r="AE2" t="n">
-        <v>4467000</v>
+        <v>116480000</v>
       </c>
       <c r="AF2" t="n">
-        <v>5670000</v>
+        <v>8210000</v>
       </c>
       <c r="AG2" t="n">
-        <v>651832000</v>
+        <v>502776000</v>
       </c>
       <c r="AH2" t="n">
-        <v>17528000</v>
+        <v>29938000</v>
       </c>
       <c r="AI2" t="n">
-        <v>500549000</v>
+        <v>343968000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>6471000</v>
+        <v>9147000</v>
       </c>
       <c r="AK2" t="n">
-        <v>494078000</v>
+        <v>334821000</v>
       </c>
       <c r="AL2" t="n">
-        <v>4273000</v>
+        <v>8651000</v>
       </c>
       <c r="AM2" t="n">
-        <v>5091000</v>
+        <v>761000</v>
       </c>
       <c r="AN2" t="n">
-        <v>56132000</v>
+        <v>67324000</v>
       </c>
       <c r="AO2" t="n">
-        <v>274000</v>
+        <v>953000</v>
       </c>
       <c r="AP2" t="n">
-        <v>55858000</v>
+        <v>66371000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>615435000</v>
+        <v>815193000</v>
       </c>
       <c r="AR2" t="n">
-        <v>459786000</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+        <v>508935000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>-3000</v>
+      </c>
       <c r="AT2" t="n">
-        <v>14667000</v>
+        <v>5401000</v>
       </c>
       <c r="AU2" t="n">
-        <v>318000</v>
+        <v>317000</v>
       </c>
       <c r="AV2" t="n">
-        <v>318000</v>
+        <v>317000</v>
       </c>
       <c r="AW2" t="n">
-        <v>22998000</v>
+        <v>39685000</v>
       </c>
       <c r="AX2" t="n">
-        <v>27259000</v>
+        <v>8733000</v>
       </c>
       <c r="AY2" t="n">
-        <v>20901000</v>
+        <v>2633000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6358000</v>
+        <v>6100000</v>
       </c>
       <c r="BA2" t="n">
-        <v>370423000</v>
+        <v>426923000</v>
       </c>
       <c r="BB2" t="n">
-        <v>-41935000</v>
+        <v>-21346000</v>
       </c>
       <c r="BC2" t="n">
-        <v>412358000</v>
+        <v>448269000</v>
       </c>
       <c r="BD2" t="n">
-        <v>198230000</v>
+        <v>244225000</v>
       </c>
       <c r="BE2" t="n">
-        <v>155770000</v>
+        <v>136678000</v>
       </c>
       <c r="BF2" t="n">
-        <v>9015000</v>
+        <v>16890000</v>
       </c>
       <c r="BG2" t="n">
-        <v>20058000</v>
+        <v>21564000</v>
       </c>
       <c r="BH2" t="n">
-        <v>29285000</v>
+        <v>28912000</v>
       </c>
       <c r="BI2" t="n">
         <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>155649000</v>
-      </c>
-      <c r="BK2" t="inlineStr"/>
+        <v>306261000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>2000</v>
+      </c>
       <c r="BL2" t="n">
-        <v>12450000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>160000</v>
-      </c>
-      <c r="BN2" t="inlineStr"/>
+        <v>5189000</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>197000</v>
+      </c>
       <c r="BO2" t="n">
-        <v>29880000</v>
+        <v>87449000</v>
       </c>
       <c r="BP2" t="n">
-        <v>7594000</v>
+        <v>7927000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2475000</v>
+        <v>10758000</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>4106000</v>
       </c>
       <c r="BS2" t="n">
-        <v>19811000</v>
+        <v>72387000</v>
       </c>
       <c r="BT2" t="n">
-        <v>38035000</v>
+        <v>25767000</v>
       </c>
       <c r="BU2" t="n">
-        <v>342000</v>
+        <v>3714000</v>
       </c>
       <c r="BV2" t="n">
-        <v>65407000</v>
+        <v>127869000</v>
       </c>
       <c r="BW2" t="n">
-        <v>9375000</v>
-      </c>
-      <c r="BX2" t="inlineStr"/>
+        <v>61462000</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>75000</v>
+      </c>
       <c r="BY2" t="n">
-        <v>9375000</v>
+        <v>61387000</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>9375000</v>
+        <v>61387000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>68773650</v>
@@ -1976,47 +1988,47 @@
         <v>68773650</v>
       </c>
       <c r="D3" t="n">
-        <v>530976000</v>
+        <v>482036000</v>
       </c>
       <c r="E3" t="n">
-        <v>550117000</v>
+        <v>521181000</v>
       </c>
       <c r="F3" t="n">
-        <v>-64348000</v>
+        <v>8777000</v>
       </c>
       <c r="G3" t="n">
-        <v>491780000</v>
+        <v>529309000</v>
       </c>
       <c r="H3" t="n">
-        <v>-211241000</v>
+        <v>-39995000</v>
       </c>
       <c r="I3" t="n">
-        <v>-64348000</v>
+        <v>8777000</v>
       </c>
       <c r="J3" t="n">
-        <v>16885000</v>
+        <v>18374000</v>
       </c>
       <c r="K3" t="n">
-        <v>-41452000</v>
+        <v>26502000</v>
       </c>
       <c r="L3" t="n">
-        <v>-41452000</v>
+        <v>220338000</v>
       </c>
       <c r="M3" t="n">
-        <v>-40693000</v>
+        <v>26359000</v>
       </c>
       <c r="N3" t="n">
-        <v>759000</v>
+        <v>-143000</v>
       </c>
       <c r="O3" t="n">
-        <v>-41452000</v>
+        <v>26502000</v>
       </c>
       <c r="P3" t="n">
         <v>-31004000</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>-145046000</v>
+        <v>-77092000</v>
       </c>
       <c r="S3" t="n">
         <v>4616000</v>
@@ -2028,177 +2040,179 @@
         <v>129982000</v>
       </c>
       <c r="V3" t="n">
-        <v>685883000</v>
+        <v>756617000</v>
       </c>
       <c r="W3" t="n">
-        <v>14479000</v>
+        <v>209393000</v>
       </c>
       <c r="X3" t="n">
-        <v>592000</v>
+        <v>480000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>79000</v>
+        <v>89000</v>
       </c>
       <c r="AA3" t="n">
-        <v>2595000</v>
+        <v>3411000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>860000</v>
       </c>
       <c r="AC3" t="n">
-        <v>9611000</v>
+        <v>203644000</v>
       </c>
       <c r="AD3" t="n">
-        <v>9611000</v>
+        <v>9808000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>193836000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1602000</v>
+        <v>909000</v>
       </c>
       <c r="AG3" t="n">
-        <v>671404000</v>
+        <v>547224000</v>
       </c>
       <c r="AH3" t="n">
-        <v>15685000</v>
+        <v>23665000</v>
       </c>
       <c r="AI3" t="n">
-        <v>540506000</v>
+        <v>317537000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>7274000</v>
+        <v>8566000</v>
       </c>
       <c r="AK3" t="n">
-        <v>533232000</v>
+        <v>308971000</v>
       </c>
       <c r="AL3" t="n">
-        <v>4564000</v>
+        <v>7220000</v>
       </c>
       <c r="AM3" t="n">
-        <v>2307000</v>
+        <v>1729000</v>
       </c>
       <c r="AN3" t="n">
-        <v>60502000</v>
+        <v>62269000</v>
       </c>
       <c r="AO3" t="n">
-        <v>2366000</v>
+        <v>721000</v>
       </c>
       <c r="AP3" t="n">
-        <v>58136000</v>
+        <v>61548000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>645190000</v>
+        <v>782976000</v>
       </c>
       <c r="AR3" t="n">
-        <v>185028000</v>
+        <v>275748000</v>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>22539000</v>
+        <v>21518000</v>
       </c>
       <c r="AU3" t="n">
-        <v>318000</v>
+        <v>317000</v>
       </c>
       <c r="AV3" t="n">
-        <v>318000</v>
+        <v>317000</v>
       </c>
       <c r="AW3" t="n">
-        <v>31002000</v>
+        <v>36336000</v>
       </c>
       <c r="AX3" t="n">
-        <v>22896000</v>
+        <v>17725000</v>
       </c>
       <c r="AY3" t="n">
-        <v>16796000</v>
+        <v>11525000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6100000</v>
+        <v>6200000</v>
       </c>
       <c r="BA3" t="n">
-        <v>89994000</v>
+        <v>175649000</v>
       </c>
       <c r="BB3" t="n">
-        <v>-26958000</v>
+        <v>-28756000</v>
       </c>
       <c r="BC3" t="n">
-        <v>116952000</v>
+        <v>204405000</v>
       </c>
       <c r="BD3" t="n">
-        <v>71733000</v>
+        <v>155990000</v>
       </c>
       <c r="BE3" t="n">
-        <v>4464000</v>
+        <v>7114000</v>
       </c>
       <c r="BF3" t="n">
-        <v>11879000</v>
+        <v>17014000</v>
       </c>
       <c r="BG3" t="n">
-        <v>25977000</v>
+        <v>24258000</v>
       </c>
       <c r="BH3" t="n">
-        <v>2899000</v>
+        <v>29000</v>
       </c>
       <c r="BI3" t="n">
         <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>460163000</v>
+        <v>507229000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1000</v>
+        <v>-1000</v>
       </c>
       <c r="BL3" t="n">
-        <v>326490000</v>
+        <v>281503000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1467000</v>
-      </c>
-      <c r="BN3" t="inlineStr"/>
+        <v>541000</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0</v>
+      </c>
       <c r="BO3" t="n">
-        <v>48376000</v>
+        <v>96560000</v>
       </c>
       <c r="BP3" t="n">
-        <v>6389000</v>
+        <v>3759000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3230000</v>
+        <v>12123000</v>
       </c>
       <c r="BR3" t="n">
-        <v>303000</v>
+        <v>632000</v>
       </c>
       <c r="BS3" t="n">
-        <v>38454000</v>
+        <v>80046000</v>
       </c>
       <c r="BT3" t="n">
-        <v>21634000</v>
+        <v>19415000</v>
       </c>
       <c r="BU3" t="n">
-        <v>372000</v>
+        <v>2713000</v>
       </c>
       <c r="BV3" t="n">
-        <v>59567000</v>
+        <v>85727000</v>
       </c>
       <c r="BW3" t="n">
-        <v>2256000</v>
+        <v>20771000</v>
       </c>
       <c r="BX3" t="inlineStr"/>
       <c r="BY3" t="n">
-        <v>2256000</v>
+        <v>20771000</v>
       </c>
       <c r="BZ3" t="n">
-        <v>900000</v>
+        <v>200000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1356000</v>
+        <v>20571000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>68773650</v>
@@ -2207,47 +2221,47 @@
         <v>68773650</v>
       </c>
       <c r="D4" t="n">
-        <v>482036000</v>
+        <v>530976000</v>
       </c>
       <c r="E4" t="n">
-        <v>521181000</v>
+        <v>550117000</v>
       </c>
       <c r="F4" t="n">
-        <v>8777000</v>
+        <v>-64348000</v>
       </c>
       <c r="G4" t="n">
-        <v>529309000</v>
+        <v>491780000</v>
       </c>
       <c r="H4" t="n">
-        <v>-39995000</v>
+        <v>-211241000</v>
       </c>
       <c r="I4" t="n">
-        <v>8777000</v>
+        <v>-64348000</v>
       </c>
       <c r="J4" t="n">
-        <v>18374000</v>
+        <v>16885000</v>
       </c>
       <c r="K4" t="n">
-        <v>26502000</v>
+        <v>-41452000</v>
       </c>
       <c r="L4" t="n">
-        <v>220338000</v>
+        <v>-41452000</v>
       </c>
       <c r="M4" t="n">
-        <v>26359000</v>
+        <v>-40693000</v>
       </c>
       <c r="N4" t="n">
-        <v>-143000</v>
+        <v>759000</v>
       </c>
       <c r="O4" t="n">
-        <v>26502000</v>
+        <v>-41452000</v>
       </c>
       <c r="P4" t="n">
         <v>-31004000</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>-77092000</v>
+        <v>-145046000</v>
       </c>
       <c r="S4" t="n">
         <v>4616000</v>
@@ -2259,179 +2273,177 @@
         <v>129982000</v>
       </c>
       <c r="V4" t="n">
-        <v>756617000</v>
+        <v>685883000</v>
       </c>
       <c r="W4" t="n">
-        <v>209393000</v>
+        <v>14479000</v>
       </c>
       <c r="X4" t="n">
-        <v>480000</v>
+        <v>592000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>89000</v>
+        <v>79000</v>
       </c>
       <c r="AA4" t="n">
-        <v>3411000</v>
+        <v>2595000</v>
       </c>
       <c r="AB4" t="n">
-        <v>860000</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>203644000</v>
+        <v>9611000</v>
       </c>
       <c r="AD4" t="n">
-        <v>9808000</v>
+        <v>9611000</v>
       </c>
       <c r="AE4" t="n">
-        <v>193836000</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>909000</v>
+        <v>1602000</v>
       </c>
       <c r="AG4" t="n">
-        <v>547224000</v>
+        <v>671404000</v>
       </c>
       <c r="AH4" t="n">
-        <v>23665000</v>
+        <v>15685000</v>
       </c>
       <c r="AI4" t="n">
-        <v>317537000</v>
+        <v>540506000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>8566000</v>
+        <v>7274000</v>
       </c>
       <c r="AK4" t="n">
-        <v>308971000</v>
+        <v>533232000</v>
       </c>
       <c r="AL4" t="n">
-        <v>7220000</v>
+        <v>4564000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1729000</v>
+        <v>2307000</v>
       </c>
       <c r="AN4" t="n">
-        <v>62269000</v>
+        <v>60502000</v>
       </c>
       <c r="AO4" t="n">
-        <v>721000</v>
+        <v>2366000</v>
       </c>
       <c r="AP4" t="n">
-        <v>61548000</v>
+        <v>58136000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>782976000</v>
+        <v>645190000</v>
       </c>
       <c r="AR4" t="n">
-        <v>275748000</v>
+        <v>185028000</v>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>21518000</v>
+        <v>22539000</v>
       </c>
       <c r="AU4" t="n">
-        <v>317000</v>
+        <v>318000</v>
       </c>
       <c r="AV4" t="n">
-        <v>317000</v>
+        <v>318000</v>
       </c>
       <c r="AW4" t="n">
-        <v>36336000</v>
+        <v>31002000</v>
       </c>
       <c r="AX4" t="n">
-        <v>17725000</v>
+        <v>22896000</v>
       </c>
       <c r="AY4" t="n">
-        <v>11525000</v>
+        <v>16796000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6200000</v>
+        <v>6100000</v>
       </c>
       <c r="BA4" t="n">
-        <v>175649000</v>
+        <v>89994000</v>
       </c>
       <c r="BB4" t="n">
-        <v>-28756000</v>
+        <v>-26958000</v>
       </c>
       <c r="BC4" t="n">
-        <v>204405000</v>
+        <v>116952000</v>
       </c>
       <c r="BD4" t="n">
-        <v>155990000</v>
+        <v>71733000</v>
       </c>
       <c r="BE4" t="n">
-        <v>7114000</v>
+        <v>4464000</v>
       </c>
       <c r="BF4" t="n">
-        <v>17014000</v>
+        <v>11879000</v>
       </c>
       <c r="BG4" t="n">
-        <v>24258000</v>
+        <v>25977000</v>
       </c>
       <c r="BH4" t="n">
-        <v>29000</v>
+        <v>2899000</v>
       </c>
       <c r="BI4" t="n">
         <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>507229000</v>
+        <v>460163000</v>
       </c>
       <c r="BK4" t="n">
-        <v>-1000</v>
+        <v>1000</v>
       </c>
       <c r="BL4" t="n">
-        <v>281503000</v>
+        <v>326490000</v>
       </c>
       <c r="BM4" t="n">
-        <v>541000</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>0</v>
-      </c>
+        <v>1467000</v>
+      </c>
+      <c r="BN4" t="inlineStr"/>
       <c r="BO4" t="n">
-        <v>96560000</v>
+        <v>48376000</v>
       </c>
       <c r="BP4" t="n">
-        <v>3759000</v>
+        <v>6389000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>12123000</v>
+        <v>3230000</v>
       </c>
       <c r="BR4" t="n">
-        <v>632000</v>
+        <v>303000</v>
       </c>
       <c r="BS4" t="n">
-        <v>80046000</v>
+        <v>38454000</v>
       </c>
       <c r="BT4" t="n">
-        <v>19415000</v>
+        <v>21634000</v>
       </c>
       <c r="BU4" t="n">
-        <v>2713000</v>
+        <v>372000</v>
       </c>
       <c r="BV4" t="n">
-        <v>85727000</v>
+        <v>59567000</v>
       </c>
       <c r="BW4" t="n">
-        <v>20771000</v>
+        <v>2256000</v>
       </c>
       <c r="BX4" t="inlineStr"/>
       <c r="BY4" t="n">
-        <v>20771000</v>
+        <v>2256000</v>
       </c>
       <c r="BZ4" t="n">
-        <v>200000</v>
+        <v>900000</v>
       </c>
       <c r="CA4" t="n">
-        <v>20571000</v>
+        <v>1356000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>68773650</v>
@@ -2440,49 +2452,47 @@
         <v>68773650</v>
       </c>
       <c r="D5" t="n">
-        <v>389914000</v>
+        <v>489170000</v>
       </c>
       <c r="E5" t="n">
-        <v>500870000</v>
+        <v>533484000</v>
       </c>
       <c r="F5" t="n">
-        <v>122303000</v>
+        <v>-106362000</v>
       </c>
       <c r="G5" t="n">
-        <v>582337000</v>
+        <v>419442000</v>
       </c>
       <c r="H5" t="n">
-        <v>-196515000</v>
+        <v>-496183000</v>
       </c>
       <c r="I5" t="n">
-        <v>122303000</v>
+        <v>-106362000</v>
       </c>
       <c r="J5" t="n">
-        <v>49569000</v>
+        <v>34939000</v>
       </c>
       <c r="K5" t="n">
-        <v>131036000</v>
+        <v>-79103000</v>
       </c>
       <c r="L5" t="n">
-        <v>247516000</v>
+        <v>-74636000</v>
       </c>
       <c r="M5" t="n">
-        <v>130771000</v>
+        <v>-78592000</v>
       </c>
       <c r="N5" t="n">
-        <v>-265000</v>
+        <v>511000</v>
       </c>
       <c r="O5" t="n">
-        <v>131036000</v>
+        <v>-79103000</v>
       </c>
       <c r="P5" t="n">
         <v>-31004000</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>27442000</v>
+        <v>-182697000</v>
       </c>
       <c r="S5" t="n">
         <v>4616000</v>
@@ -2494,178 +2504,168 @@
         <v>129982000</v>
       </c>
       <c r="V5" t="n">
-        <v>684422000</v>
+        <v>694027000</v>
       </c>
       <c r="W5" t="n">
-        <v>181646000</v>
+        <v>42195000</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>14238000</v>
-      </c>
+        <v>542000</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>64000</v>
+        <v>68000</v>
       </c>
       <c r="AA5" t="n">
-        <v>2232000</v>
+        <v>2980000</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>156902000</v>
+        <v>32935000</v>
       </c>
       <c r="AD5" t="n">
-        <v>40422000</v>
+        <v>28468000</v>
       </c>
       <c r="AE5" t="n">
-        <v>116480000</v>
+        <v>4467000</v>
       </c>
       <c r="AF5" t="n">
-        <v>8210000</v>
+        <v>5670000</v>
       </c>
       <c r="AG5" t="n">
-        <v>502776000</v>
+        <v>651832000</v>
       </c>
       <c r="AH5" t="n">
-        <v>29938000</v>
+        <v>17528000</v>
       </c>
       <c r="AI5" t="n">
-        <v>343968000</v>
+        <v>500549000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>9147000</v>
+        <v>6471000</v>
       </c>
       <c r="AK5" t="n">
-        <v>334821000</v>
+        <v>494078000</v>
       </c>
       <c r="AL5" t="n">
-        <v>8651000</v>
+        <v>4273000</v>
       </c>
       <c r="AM5" t="n">
-        <v>761000</v>
+        <v>5091000</v>
       </c>
       <c r="AN5" t="n">
-        <v>67324000</v>
+        <v>56132000</v>
       </c>
       <c r="AO5" t="n">
-        <v>953000</v>
+        <v>274000</v>
       </c>
       <c r="AP5" t="n">
-        <v>66371000</v>
+        <v>55858000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>815193000</v>
+        <v>615435000</v>
       </c>
       <c r="AR5" t="n">
-        <v>508935000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>-3000</v>
-      </c>
+        <v>459786000</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>5401000</v>
+        <v>14667000</v>
       </c>
       <c r="AU5" t="n">
-        <v>317000</v>
+        <v>318000</v>
       </c>
       <c r="AV5" t="n">
-        <v>317000</v>
+        <v>318000</v>
       </c>
       <c r="AW5" t="n">
-        <v>39685000</v>
+        <v>22998000</v>
       </c>
       <c r="AX5" t="n">
-        <v>8733000</v>
+        <v>27259000</v>
       </c>
       <c r="AY5" t="n">
-        <v>2633000</v>
+        <v>20901000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6100000</v>
+        <v>6358000</v>
       </c>
       <c r="BA5" t="n">
-        <v>426923000</v>
+        <v>370423000</v>
       </c>
       <c r="BB5" t="n">
-        <v>-21346000</v>
+        <v>-41935000</v>
       </c>
       <c r="BC5" t="n">
-        <v>448269000</v>
+        <v>412358000</v>
       </c>
       <c r="BD5" t="n">
-        <v>244225000</v>
+        <v>198230000</v>
       </c>
       <c r="BE5" t="n">
-        <v>136678000</v>
+        <v>155770000</v>
       </c>
       <c r="BF5" t="n">
-        <v>16890000</v>
+        <v>9015000</v>
       </c>
       <c r="BG5" t="n">
-        <v>21564000</v>
+        <v>20058000</v>
       </c>
       <c r="BH5" t="n">
-        <v>28912000</v>
+        <v>29285000</v>
       </c>
       <c r="BI5" t="n">
         <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>306261000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>2000</v>
-      </c>
+        <v>155649000</v>
+      </c>
+      <c r="BK5" t="inlineStr"/>
       <c r="BL5" t="n">
+        <v>12450000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>160000</v>
+      </c>
+      <c r="BN5" t="inlineStr"/>
+      <c r="BO5" t="n">
+        <v>29880000</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>7594000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>2475000</v>
+      </c>
+      <c r="BR5" t="n">
         <v>0</v>
       </c>
-      <c r="BM5" t="n">
-        <v>5189000</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>197000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>87449000</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>7927000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>10758000</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>4106000</v>
-      </c>
       <c r="BS5" t="n">
-        <v>72387000</v>
+        <v>19811000</v>
       </c>
       <c r="BT5" t="n">
-        <v>25767000</v>
+        <v>38035000</v>
       </c>
       <c r="BU5" t="n">
-        <v>3714000</v>
+        <v>342000</v>
       </c>
       <c r="BV5" t="n">
-        <v>127869000</v>
+        <v>65407000</v>
       </c>
       <c r="BW5" t="n">
-        <v>61462000</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>75000</v>
-      </c>
+        <v>9375000</v>
+      </c>
+      <c r="BX5" t="inlineStr"/>
       <c r="BY5" t="n">
-        <v>61387000</v>
+        <v>9375000</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>61387000</v>
+        <v>9375000</v>
       </c>
     </row>
   </sheetData>
@@ -2901,524 +2901,524 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-45651000</v>
+        <v>-140505000</v>
       </c>
       <c r="C2" t="n">
-        <v>-75668000</v>
+        <v>-114305000</v>
       </c>
       <c r="D2" t="n">
-        <v>12083000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>206872000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>62761000</v>
+      </c>
       <c r="F2" t="n">
-        <v>-132999000</v>
+        <v>-132455000</v>
       </c>
       <c r="G2" t="n">
-        <v>9578000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3293000</v>
-      </c>
+        <v>61387000</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>3724000</v>
-      </c>
-      <c r="J2" t="n">
+        <v>131604000</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>-70217000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>110779000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-18845000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-12075000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>62761000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>62761000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>92567000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>92567000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-114305000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>206872000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-172946000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1797000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>254000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1797000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1797000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-11118000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-11118000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-132455000</v>
+      </c>
+      <c r="AC2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
-        <v>2561000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-85940000</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
-        <v>-15325000</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
-        <v>-63585000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-63585000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-75668000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>12083000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1153000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>780000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1364000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>126662000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>126662000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-15000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-15000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-132486000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>513000</v>
-      </c>
       <c r="AD2" t="n">
-        <v>-132999000</v>
+        <v>-132455000</v>
       </c>
       <c r="AE2" t="n">
-        <v>87348000</v>
+        <v>-8050000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-3815000</v>
+        <v>-23077000</v>
       </c>
       <c r="AG2" t="n">
-        <v>52735000</v>
+        <v>-8580000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-940000</v>
+        <v>49720000</v>
       </c>
       <c r="AI2" t="n">
-        <v>28361000</v>
+        <v>17335000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18496000</v>
+        <v>-11708000</v>
       </c>
       <c r="AK2" t="n">
-        <v>2974000</v>
+        <v>-72540000</v>
       </c>
       <c r="AL2" t="n">
-        <v>34869000</v>
+        <v>18267000</v>
       </c>
       <c r="AM2" t="n">
-        <v>14852000</v>
+        <v>14692000</v>
       </c>
       <c r="AN2" t="n">
-        <v>14852000</v>
+        <v>14692000</v>
       </c>
       <c r="AO2" t="n">
-        <v>4934000</v>
+        <v>-754000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1099000</v>
+        <v>500000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-6157000</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>-24570000</v>
+        <v>-15123000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-54237000</v>
+        <v>-226672000</v>
       </c>
       <c r="C3" t="n">
-        <v>-139589000</v>
+        <v>-378294000</v>
       </c>
       <c r="D3" t="n">
-        <v>57035000</v>
+        <v>468374000</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>446000</v>
       </c>
       <c r="F3" t="n">
-        <v>-71135000</v>
+        <v>-166650000</v>
       </c>
       <c r="G3" t="n">
-        <v>7018000</v>
+        <v>27475000</v>
       </c>
       <c r="H3" t="n">
-        <v>6168000</v>
+        <v>-2000</v>
       </c>
       <c r="I3" t="n">
-        <v>21311000</v>
+        <v>61387000</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-20461000</v>
+        <v>-33910000</v>
       </c>
       <c r="L3" t="n">
-        <v>-103938000</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
+        <v>16556000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-35619000</v>
+      </c>
       <c r="N3" t="n">
-        <v>-5511000</v>
+        <v>-25617000</v>
       </c>
       <c r="O3" t="n">
+        <v>446000</v>
+      </c>
+      <c r="P3" t="n">
+        <v>446000</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>90080000</v>
+      </c>
+      <c r="R3" t="n">
+        <v>90080000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-378294000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>468374000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>9556000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>32133000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>544000</v>
+      </c>
+      <c r="X3" t="n">
+        <v>130350000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>130350000</v>
+      </c>
+      <c r="Z3" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="n">
+      <c r="AA3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-82554000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-82554000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-139589000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>57035000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>66579000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>5775000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>115000</v>
-      </c>
-      <c r="X3" t="n">
-        <v>127360000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>127360000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-174000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-174000</v>
-      </c>
       <c r="AB3" t="n">
-        <v>-67892000</v>
+        <v>-166347000</v>
       </c>
       <c r="AC3" t="n">
-        <v>3243000</v>
+        <v>303000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-71135000</v>
+        <v>-166650000</v>
       </c>
       <c r="AE3" t="n">
-        <v>16898000</v>
+        <v>-60022000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-1632000</v>
+        <v>-1772000</v>
       </c>
       <c r="AG3" t="n">
-        <v>55806000</v>
+        <v>9857000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>27013000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-16673000</v>
+        <v>-3689000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>48184000</v>
+        <v>-9111000</v>
       </c>
       <c r="AK3" t="n">
-        <v>21042000</v>
+        <v>-1724000</v>
       </c>
       <c r="AL3" t="n">
-        <v>35983000</v>
+        <v>40626000</v>
       </c>
       <c r="AM3" t="n">
-        <v>13755000</v>
+        <v>21539000</v>
       </c>
       <c r="AN3" t="n">
-        <v>13755000</v>
+        <v>21539000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1308000</v>
+        <v>1150000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-6214000</v>
+        <v>-205000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-14730000</v>
+        <v>-9960000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-69083000</v>
+        <v>-123418000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-226672000</v>
+        <v>-54237000</v>
       </c>
       <c r="C4" t="n">
-        <v>-378294000</v>
+        <v>-139589000</v>
       </c>
       <c r="D4" t="n">
-        <v>468374000</v>
+        <v>57035000</v>
       </c>
       <c r="E4" t="n">
-        <v>446000</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-166650000</v>
+        <v>-71135000</v>
       </c>
       <c r="G4" t="n">
-        <v>27475000</v>
+        <v>7018000</v>
       </c>
       <c r="H4" t="n">
-        <v>-2000</v>
+        <v>6168000</v>
       </c>
       <c r="I4" t="n">
-        <v>61387000</v>
+        <v>21311000</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-33910000</v>
+        <v>-20461000</v>
       </c>
       <c r="L4" t="n">
-        <v>16556000</v>
-      </c>
-      <c r="M4" t="n">
-        <v>-35619000</v>
-      </c>
+        <v>-103938000</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>-25617000</v>
+        <v>-5511000</v>
       </c>
       <c r="O4" t="n">
-        <v>446000</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>446000</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>90080000</v>
+        <v>-82554000</v>
       </c>
       <c r="R4" t="n">
-        <v>90080000</v>
+        <v>-82554000</v>
       </c>
       <c r="S4" t="n">
-        <v>-378294000</v>
+        <v>-139589000</v>
       </c>
       <c r="T4" t="n">
-        <v>468374000</v>
+        <v>57035000</v>
       </c>
       <c r="U4" t="n">
-        <v>9556000</v>
+        <v>66579000</v>
       </c>
       <c r="V4" t="n">
-        <v>32133000</v>
+        <v>5775000</v>
       </c>
       <c r="W4" t="n">
-        <v>544000</v>
+        <v>115000</v>
       </c>
       <c r="X4" t="n">
-        <v>130350000</v>
+        <v>127360000</v>
       </c>
       <c r="Y4" t="n">
-        <v>130350000</v>
+        <v>127360000</v>
       </c>
       <c r="Z4" t="n">
+        <v>-174000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-174000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-67892000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3243000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-71135000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>16898000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-1632000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>55806000</v>
+      </c>
+      <c r="AH4" t="n">
         <v>0</v>
       </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-166347000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>303000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-166650000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-60022000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-1772000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>9857000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>27013000</v>
-      </c>
       <c r="AI4" t="n">
-        <v>-3689000</v>
+        <v>-16673000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-9111000</v>
+        <v>48184000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-1724000</v>
+        <v>21042000</v>
       </c>
       <c r="AL4" t="n">
-        <v>40626000</v>
+        <v>35983000</v>
       </c>
       <c r="AM4" t="n">
-        <v>21539000</v>
+        <v>13755000</v>
       </c>
       <c r="AN4" t="n">
-        <v>21539000</v>
+        <v>13755000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1150000</v>
+        <v>-1308000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-205000</v>
+        <v>-6214000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-9960000</v>
+        <v>-14730000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-123418000</v>
+        <v>-69083000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-140505000</v>
+        <v>-45651000</v>
       </c>
       <c r="C5" t="n">
-        <v>-114305000</v>
+        <v>-75668000</v>
       </c>
       <c r="D5" t="n">
-        <v>206872000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>62761000</v>
-      </c>
+        <v>12083000</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>-132455000</v>
+        <v>-132999000</v>
       </c>
       <c r="G5" t="n">
-        <v>61387000</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>9578000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3293000</v>
+      </c>
       <c r="I5" t="n">
-        <v>131604000</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
+        <v>3724000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
       <c r="K5" t="n">
-        <v>-70217000</v>
+        <v>2561000</v>
       </c>
       <c r="L5" t="n">
-        <v>110779000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>-18845000</v>
-      </c>
+        <v>-85940000</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>-12075000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>62761000</v>
-      </c>
-      <c r="P5" t="n">
-        <v>62761000</v>
-      </c>
+        <v>-15325000</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>92567000</v>
+        <v>-63585000</v>
       </c>
       <c r="R5" t="n">
-        <v>92567000</v>
+        <v>-63585000</v>
       </c>
       <c r="S5" t="n">
-        <v>-114305000</v>
+        <v>-75668000</v>
       </c>
       <c r="T5" t="n">
-        <v>206872000</v>
+        <v>12083000</v>
       </c>
       <c r="U5" t="n">
-        <v>-172946000</v>
+        <v>1153000</v>
       </c>
       <c r="V5" t="n">
-        <v>1797000</v>
+        <v>780000</v>
       </c>
       <c r="W5" t="n">
-        <v>254000</v>
+        <v>1364000</v>
       </c>
       <c r="X5" t="n">
-        <v>1797000</v>
+        <v>126662000</v>
       </c>
       <c r="Y5" t="n">
-        <v>1797000</v>
+        <v>126662000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-11118000</v>
+        <v>-15000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-11118000</v>
+        <v>-15000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-132455000</v>
+        <v>-132486000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>513000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-132455000</v>
+        <v>-132999000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-8050000</v>
+        <v>87348000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-23077000</v>
+        <v>-3815000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-8580000</v>
+        <v>52735000</v>
       </c>
       <c r="AH5" t="n">
-        <v>49720000</v>
+        <v>-940000</v>
       </c>
       <c r="AI5" t="n">
-        <v>17335000</v>
+        <v>28361000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-11708000</v>
+        <v>18496000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-72540000</v>
+        <v>2974000</v>
       </c>
       <c r="AL5" t="n">
-        <v>18267000</v>
+        <v>34869000</v>
       </c>
       <c r="AM5" t="n">
-        <v>14692000</v>
+        <v>14852000</v>
       </c>
       <c r="AN5" t="n">
-        <v>14692000</v>
+        <v>14852000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-754000</v>
+        <v>4934000</v>
       </c>
       <c r="AP5" t="n">
-        <v>500000</v>
+        <v>-1099000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-6157000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-15123000</v>
+        <v>-24570000</v>
       </c>
     </row>
   </sheetData>
@@ -3853,172 +3853,172 @@
       </c>
       <c r="CF1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="CG1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="CH1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="CM1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="CN1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="CL1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="CM1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="CN1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="CO1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="CP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="CQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="CR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="CS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="CT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="CU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="CV1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="CW1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
         </is>
       </c>
       <c r="DN1" t="inlineStr">
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>348</v>
+        <v>296</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -4116,34 +4116,34 @@
         <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.538</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.519</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.519</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.598</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.538</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.519</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.519</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.598</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.636</v>
+        <v>0.605</v>
       </c>
       <c r="AD2" t="n">
         <v>283</v>
@@ -4161,34 +4161,34 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>0.774</v>
       </c>
       <c r="AK2" t="n">
-        <v>38513244</v>
+        <v>41126640</v>
       </c>
       <c r="AL2" t="n">
-        <v>60222619</v>
+        <v>42840716</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.518</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.778</v>
+        <v>1.77</v>
       </c>
       <c r="AO2" t="n">
         <v>11.4</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.518</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.74916</v>
+        <v>0.69828</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.05627</v>
+        <v>1.00996</v>
       </c>
       <c r="AS2" t="n">
         <v>0</v>
@@ -4205,7 +4205,7 @@
         <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.30221</v>
+        <v>0.30289</v>
       </c>
       <c r="AX2" t="n">
         <v>19246994</v>
@@ -4226,7 +4226,7 @@
         <v>0.448</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.25</v>
+        <v>1.3348213</v>
       </c>
       <c r="BE2" t="n">
         <v>1735603200</v>
@@ -4235,16 +4235,16 @@
         <v>1767139200</v>
       </c>
       <c r="BG2" t="n">
-        <v>1759190400</v>
+        <v>1774915200</v>
       </c>
       <c r="BH2" t="n">
         <v>-0.36</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0.63730574</v>
+        <v>-0.64323604</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.598</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         </is>
       </c>
       <c r="BN2" t="n">
-        <v>-8228000</v>
+        <v>-4353000</v>
       </c>
       <c r="BO2" t="n">
         <v>0.856</v>
@@ -4269,22 +4269,22 @@
         <v>0.977</v>
       </c>
       <c r="BQ2" t="n">
-        <v>67.351</v>
+        <v>291.03</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0.021</v>
+        <v>-0.01852</v>
       </c>
       <c r="BS2" t="n">
-        <v>-69723128</v>
+        <v>-66499500</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.017</v>
+        <v>-0.11</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.5494599999999999</v>
+        <v>0.55307996</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.02552</v>
+        <v>-0.01353</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
@@ -4327,131 +4327,131 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CF2" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>-0.18915999</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>-0.25249612</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>-0.49627</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>-0.4698325</v>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>finmb_129124615</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>Europe/Berlin</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
       </c>
       <c r="CK2" t="n">
-        <v>15</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>15</v>
+        <v>7200000</v>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>dr_market</t>
+        </is>
       </c>
       <c r="CM2" t="b">
         <v>0</v>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CO2" t="n">
+        <v>1782134701</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>11.152417</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>Columbus Energy S.A.          I</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>Columbus Energy S.A.</t>
+        </is>
+      </c>
+      <c r="CT2" t="n">
+        <v>15</v>
+      </c>
+      <c r="CU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>1620280800000</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>0.060000002</v>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>0.519 - 0.598</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
           <t>Frankfurt</t>
         </is>
       </c>
-      <c r="CO2" t="n">
+      <c r="DA2" t="n">
         <v>0</v>
       </c>
-      <c r="CP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>0.56 - 1.778</t>
-        </is>
-      </c>
-      <c r="CS2" t="n">
-        <v>-1.2179999</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>-0.68503934</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>-63.730576</v>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="CW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>Columbus Energy S.A.          I</t>
-        </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>Columbus Energy S.A.</t>
-        </is>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="DB2" t="n">
-        <v>1779430114</v>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
+        <v>0.07999998</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>0.15444012</v>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>finmb_129124615</t>
-        </is>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>Europe/Berlin</t>
-        </is>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
+          <t>0.518 - 1.77</t>
+        </is>
+      </c>
+      <c r="DE2" t="n">
+        <v>-1.1719999</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>-0.6621468700000001</v>
       </c>
       <c r="DG2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>dr_market</t>
-        </is>
-      </c>
-      <c r="DI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DJ2" t="b">
-        <v>0</v>
+        <v>-64.3236</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>-0.10027999</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>-0.14361</v>
       </c>
       <c r="DK2" t="n">
-        <v>1620280800000</v>
+        <v>-0.41196007</v>
       </c>
       <c r="DL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>0.56 - 0.56</t>
-        </is>
+        <v>-0.40789738</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>15</v>
       </c>
       <c r="DN2" t="inlineStr"/>
     </row>
